--- a/बजेट माग estimate/JCB log/after dashain/after dashain.xlsx
+++ b/बजेट माग estimate/JCB log/after dashain/after dashain.xlsx
@@ -5,24 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\JCB log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\JCB log\after dashain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F3A7DA-4F48-44DB-ADFE-F6CC1B9C9231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A22CEE0-8865-45B7-920F-55FE897ED21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="9" sheetId="13" r:id="rId1"/>
     <sheet name="new" sheetId="15" r:id="rId2"/>
+    <sheet name="new (2)" sheetId="16" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="adopted_rate_aggregate_10_20_mm">[1]District_Rate!$L$6</definedName>
@@ -46,8 +47,10 @@
     <definedName name="generator">[1]Equipment_Rate!$J$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'9'!$A$1:$H$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">new!$A$1:$H$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'new (2)'!$A$1:$H$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'9'!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">new!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'new (2)'!$1:$9</definedName>
     <definedName name="skilled">[1]District_Rate!$D$148</definedName>
     <definedName name="skilled_blacksmith">[1]District_Rate!$D$149</definedName>
     <definedName name="unskilled">[1]District_Rate!$D$156</definedName>
@@ -71,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="37">
   <si>
     <t>सुरु घण्टा मिटर (क)</t>
   </si>
@@ -179,6 +182,9 @@
   </si>
   <si>
     <t>अमला ढुटो बिचौरे सडक</t>
+  </si>
+  <si>
+    <t>मानेगैरो ओखरबोट सडक</t>
   </si>
 </sst>
 </file>
@@ -388,6 +394,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -396,9 +405,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1136,40 +1142,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1">
       <c r="A4" s="14"/>
@@ -1182,16 +1188,16 @@
       <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="14" t="s">
@@ -1311,7 +1317,7 @@
         <v>19233</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="J11" s="28"/>
+      <c r="J11" s="25"/>
     </row>
     <row r="12" spans="1:10" ht="20.25">
       <c r="A12" s="6">
@@ -1338,7 +1344,7 @@
         <v>25857.699999999804</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="J12" s="28"/>
+      <c r="J12" s="25"/>
     </row>
     <row r="13" spans="1:10" ht="20.25">
       <c r="A13" s="6">
@@ -1365,7 +1371,7 @@
         <v>20515.200000000048</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="J13" s="28"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1"/>
@@ -1549,40 +1555,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1">
       <c r="A4" s="14"/>
@@ -1595,16 +1601,16 @@
       <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="14" t="s">
@@ -1724,7 +1730,7 @@
         <v>21797.399999999612</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="J11" s="28"/>
+      <c r="J11" s="25"/>
     </row>
     <row r="12" spans="1:10" ht="20.25">
       <c r="A12" s="6">
@@ -1751,7 +1757,7 @@
         <v>22224.799999999224</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="J12" s="28"/>
+      <c r="J12" s="25"/>
     </row>
     <row r="13" spans="1:10" ht="20.25">
       <c r="A13" s="6">
@@ -1780,7 +1786,7 @@
       <c r="H13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="28"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1"/>
@@ -1851,6 +1857,371 @@
       <c r="G18" s="2">
         <f>SUM(G16:G17)</f>
         <v>85725.755000000005</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="10"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="9"/>
+    </row>
+    <row r="26" spans="1:8" ht="20.25">
+      <c r="B26" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="20.25">
+      <c r="B27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="H27" s="16"/>
+    </row>
+    <row r="28" spans="1:8" ht="18.75">
+      <c r="B28" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" ht="20.25">
+      <c r="C35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" ht="20.25">
+      <c r="C36" s="16"/>
+      <c r="F36" s="16"/>
+    </row>
+    <row r="37" spans="3:6" ht="18.75">
+      <c r="C37" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="18"/>
+      <c r="F37" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6">
+      <c r="C42" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="3:6">
+      <c r="C43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="4" t="str">
+        <f>E42</f>
+        <v>without vat</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:H5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="70" fitToHeight="2" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D0F189-EC1B-4A5E-B2DF-ED9DC51F4FB7}">
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="7" style="4" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="30.5703125" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="39.75" customHeight="1">
+      <c r="A1" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" spans="1:10" ht="23.25" customHeight="1">
+      <c r="A2" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="1:10" ht="23.25" customHeight="1">
+      <c r="A3" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+    </row>
+    <row r="4" spans="1:10" ht="12.75" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+    </row>
+    <row r="9" spans="1:10" s="24" customFormat="1" ht="40.5">
+      <c r="A9" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="20.25">
+      <c r="A10" s="6">
+        <v>1</v>
+      </c>
+      <c r="B10" s="12">
+        <v>66678</v>
+      </c>
+      <c r="C10" s="19">
+        <v>6959.3</v>
+      </c>
+      <c r="D10" s="20">
+        <v>6967.3</v>
+      </c>
+      <c r="E10" s="20">
+        <f>D10-C10</f>
+        <v>8</v>
+      </c>
+      <c r="F10" s="21">
+        <v>2137</v>
+      </c>
+      <c r="G10" s="1">
+        <f>F10*E10</f>
+        <v>17096</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="21">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="20.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="J11" s="25"/>
+    </row>
+    <row r="12" spans="1:10" ht="20.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="J12" s="25"/>
+    </row>
+    <row r="13" spans="1:10" ht="20.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="J13" s="25"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="2">
+        <f>SUM(G10:G13)</f>
+        <v>17096</v>
+      </c>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="2">
+        <f>G14</f>
+        <v>17096</v>
+      </c>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="2">
+        <f>0.13*G16</f>
+        <v>2222.48</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="2">
+        <f>SUM(G16:G17)</f>
+        <v>19318.48</v>
       </c>
       <c r="H18" s="3"/>
     </row>
